--- a/mental_health_forms/024_mental_wellbeing_assessment--mental_health_forms.xlsx
+++ b/mental_health_forms/024_mental_wellbeing_assessment--mental_health_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1000,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1000, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1001,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1001, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1002,_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1002, 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1003,_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1003, 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1004,_'label':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1004, 'label': 'Very Bad'}</t>
+          <t>Very Bad</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1005,_'label':_'therapy'}</t>
+          <t>therapy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1005, 'label': 'Therapy'}</t>
+          <t>Therapy</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1006,_'label':_'counselling'}</t>
+          <t>counselling</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1006, 'label': 'Counselling'}</t>
+          <t>Counselling</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1007,_'label':_'support_group'}</t>
+          <t>support_group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1007, 'label': 'Support Group'}</t>
+          <t>Support Group</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1008,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1008, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1009,_'label':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1009, 'label': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1010,_'label':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1010, 'label': 'Friend'}</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1011,_'label':_'mental_health_professional'}</t>
+          <t>mental_health_professional</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1011, 'label': 'Mental Health Professional'}</t>
+          <t>Mental Health Professional</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1012,_'label':_'self'}</t>
+          <t>self</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1012, 'label': 'Self'}</t>
+          <t>Self</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1013,_'label':_'anxiety'}</t>
+          <t>anxiety</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1013, 'label': 'Anxiety'}</t>
+          <t>Anxiety</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1014,_'label':_'depression'}</t>
+          <t>depression</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1014, 'label': 'Depression'}</t>
+          <t>Depression</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1015,_'label':_'mood'}</t>
+          <t>mood</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1015, 'label': 'Mood'}</t>
+          <t>Mood</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1016,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1016, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
